--- a/livrables/blocs_urbains_rectifies.xlsx
+++ b/livrables/blocs_urbains_rectifies.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HYPOTHÈSE : fenêtre km, traversée au plafond S1 ∧ bande</t>
+          <t>HYPOTHÈSE : fenêtre km, traversée au plafond du scénario de base ∧ bande</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HYPOTHÈSE : fenêtre km, traversée au plafond S1 ∧ bande</t>
+          <t>HYPOTHÈSE : fenêtre km, traversée au plafond du scénario de base ∧ bande</t>
         </is>
       </c>
     </row>
